--- a/wooclap/imports/06_Constraints_Part_2.xlsx
+++ b/wooclap/imports/06_Constraints_Part_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$5</definedName>

--- a/wooclap/imports/06_Constraints_Part_2.xlsx
+++ b/wooclap/imports/06_Constraints_Part_2.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L02-C05 · You must try all four choices 1, 2, 3 and 4. Which split covers every choice exactly once?</t>
+          <t>L02-C05 · At a propagation fixed point, dom(X) = {1,2,3,4}. We split into X ∈ {1,2} and X ∈ {3,4}. Propagation makes Y’s domain empty in the first branch. To find every solution, what should happen next?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Try {1,2} in one branch and {3,4} in the other.</t>
+          <t>Reject the first branch; propagate the second using its own copy of the parent domains.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Try {1,2} and {2,3}.</t>
+          <t>Reject the whole CSP: an empty domain in either branch proves both impossible.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Try {1} and {2}.</t>
+          <t>Explore the second branch, carrying over Y’s empty domain from the first.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Try {1,2,3} and {3,4}.</t>
+          <t>Restore X to {1,2,3,4} in the second branch so that no value is missed.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L02-C06 · In local search for a timetable, what might the starting timetable look like?</t>
+          <t>L02-C06 · Three exams A, B and C use slots {1,2}. The only clash rules are A ≠ B and B ≠ C. Local search starts at (A,B,C) = (1,1,2) and changes only B to 2. How does the number of violated rules change?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Only a timetable already proved to have no clashes.</t>
+          <t>It falls from 1 to 0: the clash between A and B disappears.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A complete timetable with some clashes that we try to repair.</t>
+          <t>It stays at 1: the clash moves from A–B to B–C.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>A list of every possible correct timetable.</t>
+          <t>It rises from 1 to 2: both rules are now violated.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>A proof that making a timetable is impossible.</t>
+          <t>The move is forbidden: local search cannot visit an assignment with a clash.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L02-C07 · You are rearranging a timetable and seem stuck. Why might you briefly accept a change that adds a clash?</t>
+          <t>L02-C07 · An annealing move raises the conflict count from 1 to 3. For this move, acceptance probability is 0.61 at T = 4 and 0.02 at T = 0.5. Accept when a random draw u is below that probability. Using u = 0.40, what happens?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>It guarantees the very next change solves everything.</t>
+          <t>Accept at both temperatures, because every proposed move is allowed.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>It proves the current timetable is already the best possible one.</t>
+          <t>Reject at both temperatures, because the conflict count increases.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Adding a clash is the final goal of timetable construction.</t>
+          <t>Accept only at T = 0.5: cooling makes uphill moves easier.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>It might let you reach a better arrangement after later changes.</t>
+          <t>Accept at T = 4; reject at T = 0.5. Cooling makes this uphill move less likely.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>L02-C08 · Your timetable search runs out of time without finding a solution. Does that prove no valid timetable exists? Briefly explain.</t>
+          <t>L02-C08 · Solver A exhaustively explores all branches of a finite CSP using sound pruning and finds no solution. Solver B makes 10,000 local-search moves, with restarts, and finds no solution. Which can conclude that the CSP is unsatisfiable, and why? Answer in two sentences.</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
